--- a/resources/age_structured_vzv_hun.xlsx
+++ b/resources/age_structured_vzv_hun.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CSURITA\PycharmProjects\PythonProject\counterfactual-analysis-vzv\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4317CBA3-D821-453E-90B3-D3931507B887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{584AF311-CEEF-4B3D-90E1-3DC04C1702F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,12 +16,11 @@
     <sheet name="varicella" sheetId="1" r:id="rId1"/>
     <sheet name="varicella11" sheetId="2" r:id="rId2"/>
     <sheet name="varicella16" sheetId="3" r:id="rId3"/>
-    <sheet name="Munka1" sheetId="5" r:id="rId4"/>
+    <sheet name="age_distribution" sheetId="5" r:id="rId4"/>
     <sheet name="varicella16_relative" sheetId="4" r:id="rId5"/>
-    <sheet name="Munka2" sheetId="6" r:id="rId6"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId7"/>
+    <externalReference r:id="rId6"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1445,6 +1444,2972 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="hu-HU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="percentStacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>age_distribution!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>age_distribution!$B$1:$U$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2024</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>age_distribution!$B$2:$U$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>3.4500456204379561E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.4050720262227205E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.3800426386272849E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.3038558716906516E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.5664854176964904E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.3331649916670876E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3.0825224689890813E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.1984217133975014E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.6187062836002079E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3.6424070355238557E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3.7890437289764538E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4.0113098855798959E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4.0219214183037852E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>3.9212442091330242E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>4.1970922965594369E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5.1691176470588233E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>5.231629392971246E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3.9615688339036587E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3.6464017461642163E-2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>3.975144705481784E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3E1A-4281-9232-E7B4780B96B7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>age_distribution!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>age_distribution!$B$1:$U$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2024</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>age_distribution!$B$3:$U$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>5.4174270072992699E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.4235314413870438E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.5057644940285221E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.5860705262001535E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.9243697478991594E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5.8380889854047775E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5.7986085320260464E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5.0816045913792074E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5.7459968784322794E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5.7544491378713383E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>6.2013455069678036E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>6.5348941680099359E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>5.941542884523239E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>5.8653209794837853E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5.5785803565554896E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>4.1397058823529412E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.0467252396166133E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.0400105290866017E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.5856711818707066E-2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1.2002042900919305E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-3E1A-4281-9232-E7B4780B96B7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>age_distribution!$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>age_distribution!$B$1:$U$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2024</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>age_distribution!$B$4:$U$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>7.2973692214111915E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7.2284999568705252E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.4534804296980103E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.6458310447105354E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7.7978250123578841E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7.7925357305186613E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8.5072668300774965E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7.8884438333233692E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>7.7027573848199318E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>7.9911363478983449E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>9.0028832292167224E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>8.4824141849219145E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>8.0408481073310972E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>7.5446724023825282E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>7.2528123149792775E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>7.3161764705882357E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.0966453674121407E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>6.6464859173466706E-3</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>5.970340887205495E-3</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4.8518896833503579E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-3E1A-4281-9232-E7B4780B96B7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>age_distribution!$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>age_distribution!$B$1:$U$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2024</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>age_distribution!$B$5:$U$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>0.15164993917274938</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.15694815837143103</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.1533748680479374</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.15577282214654509</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.16356895699456253</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.16925912832685219</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.1648221050285969</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.17157888443833325</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.16740852072374127</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.16318122013710962</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.1679961556943777</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.16742858652855216</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.15818160038332535</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.16284745201853076</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.14574699032958358</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.14124999999999999</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.11611421725239617</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>4.1392471703079761E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>9.3085960069332983E-3</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>7.4906367041198503E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-3E1A-4281-9232-E7B4780B96B7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>age_distribution!$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>age_distribution!$B$1:$U$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2024</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>age_distribution!$B$6:$U$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>0.17020225060827252</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.17527818511170534</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.1696230828141494</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.17046578051191916</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.17246663371230844</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.179738397050654</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.17935576518358959</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.1877503437556047</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.18460604659228858</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.18090852434041965</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.17722248918789044</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.17279285468911026</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.17306540488739819</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.16685969556585042</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.16383790540096047</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.15794117647058822</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.15515175718849841</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.13523295604106345</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>4.1792386210438466E-2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>9.7037793667007158E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-3E1A-4281-9232-E7B4780B96B7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>age_distribution!$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>age_distribution!$B$1:$U$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2024</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>age_distribution!$B$7:$U$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>0.14963503649635038</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.14586388337790046</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.14679278869041459</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.14558387344831375</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.14085516559565003</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.1542598858643503</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.15046175938993289</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.15364380940993602</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.15128042083357421</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.15788380306072985</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.15711196540124939</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.14282694289564782</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.14204000958313368</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.14423395102581071</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.14989145450957173</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.14367647058823529</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.15664936102236421</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.15300078968149514</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.13725364319188546</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4.0177051413006468E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-3E1A-4281-9232-E7B4780B96B7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>age_distribution!$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>6</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>age_distribution!$B$1:$U$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2024</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>age_distribution!$B$8:$U$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>0.1078353102189781</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.10471836453032002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.10655517148593546</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.10471822476106778</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.10659911023232822</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.10395939599010151</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.10230508306717176</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.1050995396664076</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.10954390427192323</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.11079565127068762</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.10867371456030754</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.10717966334592924</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.10361763296597988</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.10626240900066182</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.1171633445168081</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.11227941176470588</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.14037539936102236</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.13970781784680178</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.15651280734416126</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.13747020769492679</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-3E1A-4281-9232-E7B4780B96B7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>age_distribution!$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>7</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>age_distribution!$B$1:$U$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2024</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>age_distribution!$B$9:$U$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>6.9438108272506086E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.2322090916932631E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.1432740670212989E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.4566626386905412E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.0108749382105781E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5.8885914852785215E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5.848126965262819E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5.8946613259998802E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6.1419735244811841E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>6.2599542967938515E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>6.1292647765497359E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>6.1623021430647677E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>6.4296837565884044E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>6.5891793514228983E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>7.1936056838365903E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>8.2058823529411767E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>9.8742012779552718E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.12937615161884705</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.16306092315593504</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.19773578481443649</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-3E1A-4281-9232-E7B4780B96B7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="8"/>
+          <c:order val="8"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>age_distribution!$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>8</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>age_distribution!$B$1:$U$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2024</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>age_distribution!$B$10:$U$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>4.6627889294403896E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.3517639955145349E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.5391509531596048E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.182687026255081E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.0113692535837867E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.6967829907580428E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3.9144321473668572E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4.0742512106175646E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.6649517313139486E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3.6978048611591992E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3.8659298414223928E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4.1328647305974686E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4.9622664111164352E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>5.0421906022501656E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>4.6674560884152359E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5.2058823529411762E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>6.6992811501597443E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.10430376414846013</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.12698208897733837</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.15781409601634322</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-3E1A-4281-9232-E7B4780B96B7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="9"/>
+          <c:order val="9"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>age_distribution!$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>9</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>age_distribution!$B$1:$U$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2024</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>age_distribution!$B$11:$U$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>3.4500456204379561E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.2239282325541276E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.2662016434500028E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.982533230803032E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.7953534354918437E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.5882531185293673E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.9661541508826661E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.4033000538052251E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.5724030290768252E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.2401495741292153E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.4939932724651611E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.8221864017123378E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3.1235026353617634E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>3.2428855062872269E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3.2826787711334779E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3.8235294117647062E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>4.1234025559105429E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>6.64648591734667E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>9.3021762855492074E-2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.12087163772557032</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000009-3E1A-4281-9232-E7B4780B96B7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="10"/>
+          <c:order val="10"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>age_distribution!$A$12</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>age_distribution!$B$1:$U$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2024</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>age_distribution!$B$12:$U$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>2.3608576642335767E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.5769861123091521E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.452755987001428E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.4579808854223881E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.2268907563025211E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.9468713701328216E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.8668449330263192E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.8174209362109166E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.8440372275854097E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.8004293331486738E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.6626621816434407E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.0109399360515815E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.2610206037374223E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2.4032097948378559E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.6708769159923689E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2.3235294117647059E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3.3346645367412144E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>4.5406685969992103E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>6.3876227771714714E-2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>8.3503575076608785E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000A-3E1A-4281-9232-E7B4780B96B7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="11"/>
+          <c:order val="11"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>age_distribution!$A$13</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>11</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>age_distribution!$B$1:$U$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2024</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>age_distribution!$B$13:$U$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>1.5967153284671534E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.6906754075735358E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.8856208473909713E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.856530814017357E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.7399901136925359E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.3635674965910812E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.3691846789967566E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.4826328690141687E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.474073645875484E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.2118274357731459E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.1052378664103796E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.4137356974869857E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.443459511260182E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.5387160820648577E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.611736069995395E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.7352941176470588E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.2863418530351436E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.9152408528560148E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>4.2819541631893179E-2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>5.5243445692883898E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000B-3E1A-4281-9232-E7B4780B96B7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="12"/>
+          <c:order val="12"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>age_distribution!$A$14</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>12</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="80000"/>
+                <a:lumOff val="20000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>age_distribution!$B$1:$U$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2024</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>age_distribution!$B$14:$U$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>1.1291058394160584E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.3068230828948504E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.5130503177198683E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.5626716467098758E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.3198220464656451E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.29286399676784E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.1092129045037015E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.0193100974472409E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.1330134689866466E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9.9369849733397971E-3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>8.6737145603075442E-3</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.0358586792801839E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.1619549592716818E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.1705823957643944E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.2828103414249063E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.375E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.7571884984025558E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.1584627533561464E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2.8888746228413687E-2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4.1709227102485529E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000C-3E1A-4281-9232-E7B4780B96B7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="13"/>
+          <c:order val="13"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>age_distribution!$A$15</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>13</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:lumMod val="80000"/>
+                <a:lumOff val="20000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>age_distribution!$B$1:$U$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2024</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>age_distribution!$B$15:$U$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>1.1081964720194647E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.1256792892262573E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.1673876596361227E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.9967043831703829E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.2654473554127533E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.6207262259481851E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9.5322983980786844E-3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8.758294972200634E-3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>7.1680443956298051E-3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>8.5866629734782911E-3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>6.3911580970687169E-3</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>7.5575403641360353E-3</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>9.1938188787733591E-3</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>9.5549305095962937E-3</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>9.9006644299717127E-3</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.036764705882353E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.3777955271565496E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.8491708344301132E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2.4523335687231175E-2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2.7919645897173988E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000D-3E1A-4281-9232-E7B4780B96B7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="14"/>
+          <c:order val="14"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>age_distribution!$A$16</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>14</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3">
+                <a:lumMod val="80000"/>
+                <a:lumOff val="20000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>age_distribution!$B$1:$U$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2024</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>age_distribution!$B$16:$U$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>6.8430656934306573E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7.0301043733287331E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.6519156334733914E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.8593870152696907E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8.5022244191794369E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.0146962274632592E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7.8734308846468096E-3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6.9647874693609139E-3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6.4454592751026071E-3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>6.4053735890866282E-3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4.8774627582892837E-3</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>6.6855164759664935E-3</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>7.2771921418303782E-3</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>6.9490403706154863E-3</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>6.44694427998158E-3</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>8.1617647058823527E-3</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>8.0870607028753986E-3</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.1779415635693603E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.5985106246388908E-2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1.9237316990125979E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000E-3E1A-4281-9232-E7B4780B96B7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="15"/>
+          <c:order val="15"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>age_distribution!$A$17</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>15+</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4">
+                <a:lumMod val="80000"/>
+                <a:lumOff val="20000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>age_distribution!$B$1:$U$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2024</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>age_distribution!$B$17:$U$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>3.9670772506082724E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.4509617872854311E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.1934882950758597E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.3254970888718006E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.142362827483935E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.6740568658148579E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.1026021936665921E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.7603873976206133E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.4568472166021158E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3.6320199432172288E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.6549735703988466E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.9463837433607271E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3.2762338284619073E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>3.0112508272667107E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.9636208144201041E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3.3382352941176467E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3.5343450479233228E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3.744406422742827E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3.7683764524619634E-2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4.4518215866530472E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000F-3E1A-4281-9232-E7B4780B96B7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="528228559"/>
+        <c:axId val="521084431"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="528228559"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="hu-HU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="521084431"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="521084431"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="hu-HU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="528228559"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="hu-HU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="hu-HU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="hu-HU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
       <c:tx>
         <c:rich>
           <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
@@ -2627,7 +5592,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="hu-HU"/>
@@ -3795,7 +6760,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="hu-HU"/>
@@ -9148,7 +12113,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Munka1!$B$2:$U$2</c:f>
+              <c:f>age_distribution!$B$2:$U$2</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -9239,7 +12204,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Munka1!$B$3:$U$3</c:f>
+              <c:f>age_distribution!$B$3:$U$3</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -9330,7 +12295,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Munka1!$B$4:$U$4</c:f>
+              <c:f>age_distribution!$B$4:$U$4</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -9421,7 +12386,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Munka1!$B$5:$U$5</c:f>
+              <c:f>age_distribution!$B$5:$U$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -9512,7 +12477,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Munka1!$B$6:$U$6</c:f>
+              <c:f>age_distribution!$B$6:$U$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -9854,7 +12819,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Munka1!$B$7:$U$7</c:f>
+              <c:f>age_distribution!$B$7:$U$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -9945,7 +12910,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Munka1!$B$8:$U$8</c:f>
+              <c:f>age_distribution!$B$8:$U$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -10036,7 +13001,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Munka1!$B$9:$U$9</c:f>
+              <c:f>age_distribution!$B$9:$U$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -10127,7 +13092,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Munka1!$B$10:$U$10</c:f>
+              <c:f>age_distribution!$B$10:$U$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -10218,7 +13183,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Munka1!$B$11:$U$11</c:f>
+              <c:f>age_distribution!$B$11:$U$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -10560,7 +13525,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Munka1!$B$12:$U$12</c:f>
+              <c:f>age_distribution!$B$12:$U$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -10651,7 +13616,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Munka1!$B$13:$U$13</c:f>
+              <c:f>age_distribution!$B$13:$U$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -10742,7 +13707,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Munka1!$B$14:$U$14</c:f>
+              <c:f>age_distribution!$B$14:$U$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -10833,7 +13798,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Munka1!$B$15:$U$15</c:f>
+              <c:f>age_distribution!$B$15:$U$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -10924,7 +13889,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Munka1!$B$16:$U$16</c:f>
+              <c:f>age_distribution!$B$16:$U$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -11266,7 +14231,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Munka1!$B$2:$B$17</c:f>
+              <c:f>age_distribution!$B$2:$B$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="16"/>
@@ -11565,7 +14530,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Munka1!$U$2:$U$17</c:f>
+              <c:f>age_distribution!$U$2:$U$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="16"/>
@@ -11918,6 +14883,46 @@
 </file>
 
 <file path=xl/charts/colors12.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors13.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -12781,7 +15786,7 @@
 </file>
 
 <file path=xl/charts/style10.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -12985,22 +15990,23 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -13105,8 +16111,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -13238,19 +16244,20 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -13787,6 +16794,509 @@
 </file>
 
 <file path=xl/charts/style12.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style13.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -18642,15 +22152,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>371475</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:colOff>73025</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>66675</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>377825</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>44450</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -18678,15 +22188,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>352425</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:colOff>111125</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>415925</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -18706,6 +22216,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>250824</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>196849</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Diagram 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F13D720-6517-0754-5B84-8A5778031D57}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -25151,13 +28697,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95573068-A2D9-4B8E-83AD-A1C60BB0E10E}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/resources/age_structured_vzv_hun.xlsx
+++ b/resources/age_structured_vzv_hun.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{584AF311-CEEF-4B3D-90E1-3DC04C1702F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="varicella" sheetId="1" r:id="rId1"/>
